--- a/reading/reading.xlsx
+++ b/reading/reading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkudija/Documents/GitHub/mkudija.github.io/reading/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19720CC6-C62E-8242-AE95-A048B6679870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CCED22-F227-E24E-ACE4-3CA10A41D09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14700" yWindow="740" windowWidth="14700" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Books" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="2325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4807" uniqueCount="2339">
   <si>
     <t>Title</t>
   </si>
@@ -7011,6 +7011,48 @@
   </si>
   <si>
     <t>Remember what Elon went through to get where he is.</t>
+  </si>
+  <si>
+    <t>The Art of Clear Thinking</t>
+  </si>
+  <si>
+    <t>Hasard Lee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fun book, neat fighter pilot stories, some good tips. </t>
+  </si>
+  <si>
+    <t>Reentry: SpaceX, Elon Musk, and the Reusable Rockets that Launched a Second Space Age</t>
+  </si>
+  <si>
+    <t>It was fun to read about some of what I was there for!</t>
+  </si>
+  <si>
+    <t>The Pilgrimage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I intended this to be a little spiritual preparation for walking the Camino, but it was weird and basically occult? Super confused, don't recommend. </t>
+  </si>
+  <si>
+    <t>Stunned by Scripture: How the Bible Made Me Catholic</t>
+  </si>
+  <si>
+    <t>Good read with the kids!</t>
+  </si>
+  <si>
+    <t>Not my favorite, but interesting book from Becca for our book club.</t>
+  </si>
+  <si>
+    <t>I read this slowly over the semester for our CCD class. Reading history makes you realize how messy it is, and how the Holy Spirit has guided the Church.</t>
+  </si>
+  <si>
+    <t>These were a bit hard to follow at times, but the boys enjoyed hearing these myths, and you can see how they influenced Tolkien's worldview.</t>
+  </si>
+  <si>
+    <t>This was a quick read on the occasion of his feast. Such a powerful and prophetic letter.</t>
+  </si>
+  <si>
+    <t>Many thoughts reading this that will take more time to digest, espeically about good work. It affirms a desire for the mass as primary.</t>
   </si>
 </sst>
 </file>
@@ -7020,11 +7062,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.0%;_(* \(#,##0.0\)%;_(* &quot;   -&quot;?_)"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7324,46 +7373,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -7386,15 +7436,15 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -51822,7 +51872,9 @@
       <c r="G1068" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H1068" s="3"/>
+      <c r="H1068" s="3" t="s">
+        <v>2333</v>
+      </c>
       <c r="I1068" s="3"/>
       <c r="J1068" s="3"/>
       <c r="K1068" s="3"/>
@@ -51864,7 +51916,9 @@
       <c r="G1069" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="H1069" s="3"/>
+      <c r="H1069" s="3" t="s">
+        <v>2334</v>
+      </c>
       <c r="I1069" s="3"/>
       <c r="J1069" s="3"/>
       <c r="K1069" s="3"/>
@@ -51906,7 +51960,9 @@
       <c r="G1070" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="H1070" s="3"/>
+      <c r="H1070" s="3" t="s">
+        <v>2335</v>
+      </c>
       <c r="I1070" s="3"/>
       <c r="J1070" s="3"/>
       <c r="K1070" s="3"/>
@@ -51992,7 +52048,9 @@
       <c r="G1072" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="H1072" s="3"/>
+      <c r="H1072" s="3" t="s">
+        <v>2336</v>
+      </c>
       <c r="I1072" s="3"/>
       <c r="J1072" s="3"/>
       <c r="K1072" s="3"/>
@@ -52034,7 +52092,9 @@
       <c r="G1073" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="H1073" s="3"/>
+      <c r="H1073" s="3" t="s">
+        <v>2337</v>
+      </c>
       <c r="I1073" s="3"/>
       <c r="J1073" s="3"/>
       <c r="K1073" s="3"/>
@@ -52076,7 +52136,9 @@
       <c r="G1074" s="45" t="s">
         <v>2089</v>
       </c>
-      <c r="H1074" s="3"/>
+      <c r="H1074" s="3" t="s">
+        <v>2338</v>
+      </c>
       <c r="I1074" s="3"/>
       <c r="J1074" s="3"/>
       <c r="K1074" s="3"/>
@@ -52141,14 +52203,30 @@
       <c r="Z1075" s="3"/>
     </row>
     <row r="1076" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1076" s="3"/>
-      <c r="B1076" s="3"/>
-      <c r="C1076" s="3"/>
-      <c r="D1076" s="7"/>
-      <c r="E1076" s="7"/>
-      <c r="F1076" s="7"/>
-      <c r="G1076" s="6"/>
-      <c r="H1076" s="3"/>
+      <c r="A1076" s="48" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B1076" s="3" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C1076" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1076" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1076" s="7">
+        <v>2023</v>
+      </c>
+      <c r="F1076" s="7">
+        <v>272</v>
+      </c>
+      <c r="G1076" s="45" t="s">
+        <v>2089</v>
+      </c>
+      <c r="H1076" s="3" t="s">
+        <v>2327</v>
+      </c>
       <c r="I1076" s="3"/>
       <c r="J1076" s="3"/>
       <c r="K1076" s="3"/>
@@ -52169,14 +52247,30 @@
       <c r="Z1076" s="3"/>
     </row>
     <row r="1077" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1077" s="3"/>
-      <c r="B1077" s="3"/>
-      <c r="C1077" s="3"/>
-      <c r="D1077" s="7"/>
-      <c r="E1077" s="7"/>
-      <c r="F1077" s="7"/>
-      <c r="G1077" s="6"/>
-      <c r="H1077" s="3"/>
+      <c r="A1077" s="48" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B1077" s="3" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1077" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1077" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1077" s="7">
+        <v>2024</v>
+      </c>
+      <c r="F1077" s="7">
+        <v>401</v>
+      </c>
+      <c r="G1077" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H1077" s="3" t="s">
+        <v>2329</v>
+      </c>
       <c r="I1077" s="3"/>
       <c r="J1077" s="3"/>
       <c r="K1077" s="3"/>
@@ -52197,14 +52291,30 @@
       <c r="Z1077" s="3"/>
     </row>
     <row r="1078" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1078" s="3"/>
-      <c r="B1078" s="3"/>
-      <c r="C1078" s="3"/>
-      <c r="D1078" s="7"/>
-      <c r="E1078" s="7"/>
-      <c r="F1078" s="7"/>
-      <c r="G1078" s="6"/>
-      <c r="H1078" s="3"/>
+      <c r="A1078" s="48" t="s">
+        <v>2330</v>
+      </c>
+      <c r="B1078" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1078" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1078" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1078" s="7">
+        <v>1987</v>
+      </c>
+      <c r="F1078" s="7">
+        <v>271</v>
+      </c>
+      <c r="G1078" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H1078" s="3" t="s">
+        <v>2331</v>
+      </c>
       <c r="I1078" s="3"/>
       <c r="J1078" s="3"/>
       <c r="K1078" s="3"/>
@@ -52225,13 +52335,27 @@
       <c r="Z1078" s="3"/>
     </row>
     <row r="1079" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1079" s="3"/>
-      <c r="B1079" s="3"/>
-      <c r="C1079" s="3"/>
-      <c r="D1079" s="7"/>
-      <c r="E1079" s="7"/>
-      <c r="F1079" s="7"/>
-      <c r="G1079" s="6"/>
+      <c r="A1079" s="48" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B1079" s="3" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C1079" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1079" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1079" s="7">
+        <v>2017</v>
+      </c>
+      <c r="F1079" s="7">
+        <v>144</v>
+      </c>
+      <c r="G1079" s="45" t="s">
+        <v>2089</v>
+      </c>
       <c r="H1079" s="3"/>
       <c r="I1079" s="3"/>
       <c r="J1079" s="3"/>

--- a/reading/reading.xlsx
+++ b/reading/reading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkudija/Documents/GitHub/mkudija.github.io/reading/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CCED22-F227-E24E-ACE4-3CA10A41D09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17340FCE-B1C4-2B43-BBB8-21E7DFEAAE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="14700" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Books" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4807" uniqueCount="2339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4847" uniqueCount="2357">
   <si>
     <t>Title</t>
   </si>
@@ -7053,6 +7053,60 @@
   </si>
   <si>
     <t>Many thoughts reading this that will take more time to digest, espeically about good work. It affirms a desire for the mass as primary.</t>
+  </si>
+  <si>
+    <t>Catholics and Protestants: What Can We Learn from Each Other?</t>
+  </si>
+  <si>
+    <t>Communion: Finding My Way Back to Faith</t>
+  </si>
+  <si>
+    <t>JD Vance</t>
+  </si>
+  <si>
+    <t>The Bible Is a Catholic Book</t>
+  </si>
+  <si>
+    <t>Jimmy Akin</t>
+  </si>
+  <si>
+    <t>Listening to the Law: Reflections on the Court and Constitution</t>
+  </si>
+  <si>
+    <t>Amy Coney Barrett</t>
+  </si>
+  <si>
+    <t>Munificentissimus Deus-Defining the Dogma of the Assumption</t>
+  </si>
+  <si>
+    <t>Jesus and the Jewish Roots of the Eucharist</t>
+  </si>
+  <si>
+    <t>Brant Pitre</t>
+  </si>
+  <si>
+    <t>Pope Pius XII</t>
+  </si>
+  <si>
+    <t>Fire of Love: A Historical Novel about Saint John of the Cross</t>
+  </si>
+  <si>
+    <t>By What Authority? An Evangelical Discovers Catholic Tradition</t>
+  </si>
+  <si>
+    <t>Mark Shea</t>
+  </si>
+  <si>
+    <t>José Luis Olaizola</t>
+  </si>
+  <si>
+    <t>Johnny Tremain</t>
+  </si>
+  <si>
+    <t>Esther Forbes</t>
+  </si>
+  <si>
+    <t>Jesus and the Jewish Roots of Mary</t>
   </si>
 </sst>
 </file>
@@ -7062,11 +7116,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.0%;_(* \(#,##0.0\)%;_(* &quot;   -&quot;?_)"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7373,46 +7434,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="1" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -7435,15 +7497,15 @@
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -52353,8 +52415,8 @@
       <c r="F1079" s="7">
         <v>144</v>
       </c>
-      <c r="G1079" s="45" t="s">
-        <v>2089</v>
+      <c r="G1079" s="6" t="s">
+        <v>915</v>
       </c>
       <c r="H1079" s="3"/>
       <c r="I1079" s="3"/>
@@ -52377,13 +52439,27 @@
       <c r="Z1079" s="3"/>
     </row>
     <row r="1080" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1080" s="3"/>
-      <c r="B1080" s="3"/>
-      <c r="C1080" s="3"/>
-      <c r="D1080" s="7"/>
-      <c r="E1080" s="7"/>
-      <c r="F1080" s="7"/>
-      <c r="G1080" s="6"/>
+      <c r="A1080" s="3" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B1080" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1080" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1080" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1080" s="7">
+        <v>2017</v>
+      </c>
+      <c r="F1080" s="7">
+        <v>206</v>
+      </c>
+      <c r="G1080" s="6" t="s">
+        <v>915</v>
+      </c>
       <c r="H1080" s="3"/>
       <c r="I1080" s="3"/>
       <c r="J1080" s="3"/>
@@ -52405,13 +52481,27 @@
       <c r="Z1080" s="3"/>
     </row>
     <row r="1081" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1081" s="3"/>
-      <c r="B1081" s="3"/>
-      <c r="C1081" s="3"/>
-      <c r="D1081" s="7"/>
-      <c r="E1081" s="7"/>
-      <c r="F1081" s="7"/>
-      <c r="G1081" s="6"/>
+      <c r="A1081" s="3" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B1081" s="3" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C1081" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1081" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1081" s="7">
+        <v>2026</v>
+      </c>
+      <c r="F1081" s="7">
+        <v>289</v>
+      </c>
+      <c r="G1081" s="45" t="s">
+        <v>2089</v>
+      </c>
       <c r="H1081" s="3"/>
       <c r="I1081" s="3"/>
       <c r="J1081" s="3"/>
@@ -52433,13 +52523,27 @@
       <c r="Z1081" s="3"/>
     </row>
     <row r="1082" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1082" s="3"/>
-      <c r="B1082" s="3"/>
-      <c r="C1082" s="3"/>
-      <c r="D1082" s="7"/>
-      <c r="E1082" s="7"/>
-      <c r="F1082" s="7"/>
-      <c r="G1082" s="6"/>
+      <c r="A1082" s="49" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B1082" s="3" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C1082" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1082" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1082" s="7">
+        <v>2019</v>
+      </c>
+      <c r="F1082" s="7">
+        <v>200</v>
+      </c>
+      <c r="G1082" s="6" t="s">
+        <v>915</v>
+      </c>
       <c r="H1082" s="3"/>
       <c r="I1082" s="3"/>
       <c r="J1082" s="3"/>
@@ -52461,13 +52565,27 @@
       <c r="Z1082" s="3"/>
     </row>
     <row r="1083" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1083" s="3"/>
-      <c r="B1083" s="3"/>
-      <c r="C1083" s="3"/>
-      <c r="D1083" s="7"/>
-      <c r="E1083" s="7"/>
-      <c r="F1083" s="7"/>
-      <c r="G1083" s="6"/>
+      <c r="A1083" s="49" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B1083" s="3" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C1083" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1083" s="7">
+        <v>2016</v>
+      </c>
+      <c r="E1083" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F1083" s="7">
+        <v>336</v>
+      </c>
+      <c r="G1083" s="45" t="s">
+        <v>2089</v>
+      </c>
       <c r="H1083" s="3"/>
       <c r="I1083" s="3"/>
       <c r="J1083" s="3"/>
@@ -52489,13 +52607,27 @@
       <c r="Z1083" s="3"/>
     </row>
     <row r="1084" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1084" s="3"/>
-      <c r="B1084" s="3"/>
-      <c r="C1084" s="3"/>
-      <c r="D1084" s="7"/>
-      <c r="E1084" s="7"/>
-      <c r="F1084" s="7"/>
-      <c r="G1084" s="6"/>
+      <c r="A1084" s="49" t="s">
+        <v>2347</v>
+      </c>
+      <c r="B1084" s="3" t="s">
+        <v>2348</v>
+      </c>
+      <c r="C1084" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1084" s="7">
+        <v>2016</v>
+      </c>
+      <c r="E1084" s="7">
+        <v>2016</v>
+      </c>
+      <c r="F1084" s="7">
+        <v>258</v>
+      </c>
+      <c r="G1084" s="6" t="s">
+        <v>915</v>
+      </c>
       <c r="H1084" s="3"/>
       <c r="I1084" s="3"/>
       <c r="J1084" s="3"/>
@@ -52517,13 +52649,27 @@
       <c r="Z1084" s="3"/>
     </row>
     <row r="1085" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1085" s="3"/>
-      <c r="B1085" s="3"/>
-      <c r="C1085" s="3"/>
-      <c r="D1085" s="7"/>
-      <c r="E1085" s="7"/>
-      <c r="F1085" s="7"/>
-      <c r="G1085" s="6"/>
+      <c r="A1085" s="49" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B1085" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="C1085" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D1085" s="7">
+        <v>2016</v>
+      </c>
+      <c r="E1085" s="7">
+        <v>1950</v>
+      </c>
+      <c r="F1085" s="7">
+        <v>24</v>
+      </c>
+      <c r="G1085" s="6" t="s">
+        <v>915</v>
+      </c>
       <c r="H1085" s="3"/>
       <c r="I1085" s="3"/>
       <c r="J1085" s="3"/>
@@ -52545,13 +52691,27 @@
       <c r="Z1085" s="3"/>
     </row>
     <row r="1086" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1086" s="3"/>
-      <c r="B1086" s="3"/>
-      <c r="C1086" s="3"/>
-      <c r="D1086" s="7"/>
-      <c r="E1086" s="7"/>
-      <c r="F1086" s="7"/>
-      <c r="G1086" s="6"/>
+      <c r="A1086" s="3" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B1086" s="3" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C1086" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="D1086" s="7">
+        <v>2016</v>
+      </c>
+      <c r="E1086" s="7">
+        <v>2011</v>
+      </c>
+      <c r="F1086" s="7">
+        <v>218</v>
+      </c>
+      <c r="G1086" s="45" t="s">
+        <v>2089</v>
+      </c>
       <c r="H1086" s="3"/>
       <c r="I1086" s="3"/>
       <c r="J1086" s="3"/>
@@ -52573,13 +52733,27 @@
       <c r="Z1086" s="3"/>
     </row>
     <row r="1087" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1087" s="3"/>
-      <c r="B1087" s="3"/>
-      <c r="C1087" s="3"/>
-      <c r="D1087" s="7"/>
-      <c r="E1087" s="7"/>
-      <c r="F1087" s="7"/>
-      <c r="G1087" s="6"/>
+      <c r="A1087" s="49" t="s">
+        <v>2351</v>
+      </c>
+      <c r="B1087" s="3" t="s">
+        <v>2352</v>
+      </c>
+      <c r="C1087" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="D1087" s="7">
+        <v>2016</v>
+      </c>
+      <c r="E1087" s="7">
+        <v>2013</v>
+      </c>
+      <c r="F1087" s="7">
+        <v>207</v>
+      </c>
+      <c r="G1087" s="45" t="s">
+        <v>2089</v>
+      </c>
       <c r="H1087" s="3"/>
       <c r="I1087" s="3"/>
       <c r="J1087" s="3"/>
@@ -52601,13 +52775,27 @@
       <c r="Z1087" s="3"/>
     </row>
     <row r="1088" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1088" s="3"/>
-      <c r="B1088" s="3"/>
-      <c r="C1088" s="3"/>
-      <c r="D1088" s="7"/>
-      <c r="E1088" s="7"/>
-      <c r="F1088" s="7"/>
-      <c r="G1088" s="6"/>
+      <c r="A1088" s="49" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B1088" s="3" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C1088" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1088" s="7">
+        <v>2016</v>
+      </c>
+      <c r="E1088" s="7">
+        <v>1943</v>
+      </c>
+      <c r="F1088" s="7">
+        <v>306</v>
+      </c>
+      <c r="G1088" s="6" t="s">
+        <v>915</v>
+      </c>
       <c r="H1088" s="3"/>
       <c r="I1088" s="3"/>
       <c r="J1088" s="3"/>
@@ -52629,13 +52817,27 @@
       <c r="Z1088" s="3"/>
     </row>
     <row r="1089" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1089" s="3"/>
-      <c r="B1089" s="3"/>
-      <c r="C1089" s="3"/>
-      <c r="D1089" s="7"/>
-      <c r="E1089" s="7"/>
-      <c r="F1089" s="7"/>
-      <c r="G1089" s="6"/>
+      <c r="A1089" s="49" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B1089" s="3" t="s">
+        <v>2348</v>
+      </c>
+      <c r="C1089" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1089" s="7">
+        <v>2016</v>
+      </c>
+      <c r="E1089" s="7">
+        <v>2018</v>
+      </c>
+      <c r="F1089" s="7">
+        <v>240</v>
+      </c>
+      <c r="G1089" s="45" t="s">
+        <v>2089</v>
+      </c>
       <c r="H1089" s="3"/>
       <c r="I1089" s="3"/>
       <c r="J1089" s="3"/>
